--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486818_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486818_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0953</v>
+        <v>10.4248</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6883</v>
+        <v>7.3157</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4071</v>
+        <v>3.1091</v>
       </c>
       <c r="G2" t="n">
         <v>5.0632</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5188</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3038</v>
+        <v>0.3237</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8226</v>
+        <v>0.5246</v>
       </c>
       <c r="V2" t="n">
         <v>3.3548</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6754</v>
+        <v>4.7547</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1759</v>
+        <v>3.9076</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4995</v>
+        <v>0.8471</v>
       </c>
       <c r="G3" t="n">
         <v>1.7908</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7341</v>
+        <v>1.8134</v>
       </c>
       <c r="T3" t="n">
-        <v>4.0538</v>
+        <v>1.7855</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3197</v>
+        <v>0.0279</v>
       </c>
       <c r="V3" t="n">
         <v>0.5712</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9311</v>
+        <v>1.764</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6556</v>
+        <v>-0.7731</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5867</v>
+        <v>2.5371</v>
       </c>
       <c r="G4" t="n">
         <v>0.5306</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3638</v>
+        <v>0.469</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6622</v>
+        <v>0.2204</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2983</v>
+        <v>0.2487</v>
       </c>
       <c r="V4" t="n">
         <v>0.5712</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.427</v>
+        <v>0.6574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4819</v>
+        <v>0.4888</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0549</v>
+        <v>0.1686</v>
       </c>
       <c r="G5" t="n">
         <v>1.9705</v>
@@ -844,13 +844,13 @@
         <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2926</v>
+        <v>-0.0622</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5512</v>
+        <v>0.5582</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8438</v>
+        <v>-0.6203</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2856</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3897</v>
+        <v>-0.5635</v>
       </c>
       <c r="E6" t="n">
         <v>-1.9008</v>
       </c>
       <c r="F6" t="n">
-        <v>1.511</v>
+        <v>1.3372</v>
       </c>
       <c r="G6" t="n">
         <v>0.1095</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.364</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>-0.08309999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.281</v>
+        <v>-0.4548</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3282</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8686</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.594</v>
+        <v>-2.5389</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7254</v>
+        <v>1.8993</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0022</v>
@@ -1000,13 +1000,13 @@
         <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4192</v>
+        <v>0.6482</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1303</v>
+        <v>1.1855</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7111</v>
+        <v>-0.5373</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6081</v>
+        <v>-1.9781</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5996</v>
+        <v>-2.0018</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0237</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7033</v>
+        <v>-3.1337</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3031</v>
+        <v>-0.0141</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4002</v>
+        <v>-3.1197</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0272</v>
+        <v>-2.491</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0272</v>
+        <v>-0.4271</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.0639</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6761</v>
+        <v>-0.6427</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2759</v>
+        <v>0.4131</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4002</v>
+        <v>-1.0558</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4467</v>
+        <v>0.2828</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3584</v>
+        <v>0.4892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.2065</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7242</v>
+        <v>-2.4874</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5741</v>
+        <v>-2.2799</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1502</v>
+        <v>-0.2075</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1337</v>
+        <v>-2.4834</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0141</v>
+        <v>-0.6206</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.1197</v>
+        <v>-1.8628</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.491</v>
+        <v>-1.6826</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4271</v>
+        <v>-0.3443</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0639</v>
+        <v>-1.3383</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6427</v>
+        <v>-0.8008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4131</v>
+        <v>-0.2763</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0558</v>
+        <v>-0.5245</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R9" t="n">
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4634</v>
+        <v>-0.2896</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.2756</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3803</v>
+        <v>-0.5652</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2856</v>
+        <v>0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1906</v>
+        <v>-2.9929</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1073</v>
+        <v>-2.9099</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0834</v>
+        <v>-0.083</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4834</v>
+        <v>-1.7033</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6206</v>
+        <v>-1.3031</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8628</v>
+        <v>-0.4002</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6826</v>
+        <v>-1.0272</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3443</v>
+        <v>-1.0272</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3383</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8008</v>
+        <v>-0.6761</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2763</v>
+        <v>-0.2759</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5245</v>
+        <v>-0.4002</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9929</v>
+        <v>0.062</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5518</v>
+        <v>0.0481</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.441</v>
+        <v>0.0139</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3699</v>
+        <v>-4.4099</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0027</v>
+        <v>-4.8441</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6329</v>
+        <v>0.4342</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6246</v>
@@ -1312,13 +1312,13 @@
         <v>3.0892</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6675</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2753</v>
+        <v>0.4339</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3922</v>
+        <v>0.1936</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4128</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.977699999999998</v>
+        <v>4.529499999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.087999999999999</v>
+        <v>-5.536399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>10.0656</v>
+        <v>10.0658</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.482599999999999</v>
+        <v>-1.4826</v>
       </c>
       <c r="H12" t="n">
         <v>16.207</v>
@@ -1381,7 +1381,7 @@
         <v>-7.9016</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9655000000000005</v>
+        <v>0.9655000000000002</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.4464</v>
@@ -1390,10 +1390,10 @@
         <v>16.4117</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3096</v>
+        <v>3.8616</v>
       </c>
       <c r="T12" t="n">
-        <v>4.685</v>
+        <v>5.237</v>
       </c>
       <c r="U12" t="n">
         <v>-1.3754</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6903</v>
+        <v>4.3458</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8913</v>
+        <v>2.5469</v>
       </c>
       <c r="F13" t="n">
         <v>1.7989</v>
@@ -1468,10 +1468,10 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0134</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1784</v>
+        <v>0.834</v>
       </c>
       <c r="U13" t="n">
         <v>-0.1651</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.89</v>
+        <v>3.2499</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0585</v>
+        <v>2.3687</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8315</v>
+        <v>0.8811</v>
       </c>
       <c r="G14" t="n">
         <v>3.9724</v>
@@ -1546,13 +1546,13 @@
         <v>2.7031</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0977</v>
+        <v>-0.7378</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3591</v>
+        <v>-0.0488</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7386</v>
+        <v>-0.6889</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3709</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>P. DIOP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6869</v>
+        <v>0.7139</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2387</v>
+        <v>-0.0063</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9256</v>
+        <v>0.7202</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1021</v>
+        <v>2.6544</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5588</v>
+        <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4568</v>
+        <v>2.6201</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2175</v>
+        <v>2.2283</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2698</v>
+        <v>1.0006</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4873</v>
+        <v>1.2276</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1154</v>
+        <v>0.4261</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8286</v>
+        <v>-0.9664</v>
       </c>
       <c r="O15" t="n">
-        <v>1.9441</v>
+        <v>1.3925</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3515</v>
+        <v>-2.1239</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0167</v>
+        <v>-1.2687</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3304</v>
+        <v>-0.1107</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3137</v>
+        <v>-1.158</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. DIOP</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4159</v>
+        <v>0.4634</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0063</v>
+        <v>-2.2387</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4222</v>
+        <v>2.7021</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6544</v>
+        <v>-0.1021</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0343</v>
+        <v>-0.5588</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6201</v>
+        <v>0.4568</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2283</v>
+        <v>-1.2175</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0006</v>
+        <v>0.2698</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2276</v>
+        <v>-1.4873</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4261</v>
+        <v>1.1154</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9664</v>
+        <v>-0.8286</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3925</v>
+        <v>1.9441</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1239</v>
+        <v>-1.3515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5667</v>
+        <v>-0.2068</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1107</v>
+        <v>0.3304</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.456</v>
+        <v>-0.5372</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0565</v>
+        <v>-0.1523</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9673</v>
+        <v>1.2721</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0238</v>
+        <v>-1.4244</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5062</v>
+        <v>2.2161</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7857</v>
+        <v>-1.5728</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2795</v>
+        <v>3.7889</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6535</v>
+        <v>3.2997</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4908</v>
+        <v>-0.6067</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>3.9065</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1598</v>
+        <v>-1.0837</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2765</v>
+        <v>-0.9661</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1167</v>
+        <v>-0.1176</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4082</v>
+        <v>-0.469</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4684</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0602</v>
+        <v>-0.5652</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3129</v>
+        <v>-1.5133</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.3129</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5649</v>
+        <v>-0.5938</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-1.0626</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3943</v>
+        <v>0.4688</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0076</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4082</v>
+        <v>0.3792</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6343</v>
+        <v>0.5309</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9467</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6516</v>
+        <v>-2.4844</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5983</v>
+        <v>1.7258</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2161</v>
+        <v>-0.5062</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5728</v>
+        <v>-1.7857</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7889</v>
+        <v>1.2795</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2997</v>
+        <v>0.6535</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6067</v>
+        <v>0.4908</v>
       </c>
       <c r="L19" t="n">
-        <v>3.9065</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0837</v>
+        <v>-1.1598</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9661</v>
+        <v>-2.2765</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1176</v>
+        <v>1.1167</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2633</v>
+        <v>-0.4069</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5243</v>
+        <v>-0.0487</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.739</v>
+        <v>-0.3581</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5133</v>
+        <v>1.3129</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9813</v>
+        <v>-0.9316</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7385</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2428</v>
+        <v>-0.1932</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7661</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2152</v>
+        <v>-0.1655</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5978</v>
+        <v>-1.5729</v>
       </c>
       <c r="E21" t="n">
         <v>-2.483</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8852</v>
+        <v>0.9101</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6766</v>
@@ -2092,13 +2092,13 @@
         <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0442</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0277</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0904</v>
+        <v>-3.3086</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0938</v>
+        <v>-1.163</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9967</v>
+        <v>-2.1457</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2325</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7887</v>
+        <v>-0.0069</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.607</v>
+        <v>0.3238</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1817</v>
+        <v>-0.3307</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8415</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5361</v>
+        <v>-5.4327</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1803</v>
+        <v>-6.0769</v>
       </c>
       <c r="F23" t="n">
         <v>0.6442</v>
@@ -2248,10 +2248,10 @@
         <v>2.51</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2688</v>
+        <v>-1.1654</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.497</v>
+        <v>-0.3936</v>
       </c>
       <c r="U23" t="n">
         <v>-0.7718</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.977600000000001</v>
+        <v>-3.9775</v>
       </c>
       <c r="E24" t="n">
         <v>-10.0657</v>
       </c>
       <c r="F24" t="n">
-        <v>6.0879</v>
+        <v>6.087899999999999</v>
       </c>
       <c r="G24" t="n">
         <v>1.482799999999998</v>
@@ -2326,13 +2326,13 @@
         <v>15.4463</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.3097</v>
+        <v>-3.3099</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3753</v>
+        <v>1.3754</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.6851</v>
+        <v>-4.685</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1851</v>
